--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0003T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>79.09599943935747</v>
+        <v>12.85309990889559</v>
       </c>
       <c r="D2" t="n">
-        <v>37.56860391337426</v>
+        <v>6.104898135923317</v>
       </c>
       <c r="E2" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F2" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69.98963878550994</v>
+        <v>11.37331630264537</v>
       </c>
       <c r="D3" t="n">
-        <v>26.09077039377894</v>
+        <v>4.239750188989078</v>
       </c>
       <c r="E3" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F3" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.81585449984079</v>
+        <v>6.957576356224129</v>
       </c>
       <c r="D4" t="n">
-        <v>5.438219939567653</v>
+        <v>0.8837107401797437</v>
       </c>
       <c r="E4" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F4" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.4369916379281</v>
+        <v>2.021011141163315</v>
       </c>
       <c r="D5" t="n">
-        <v>11.87234320375386</v>
+        <v>1.929255770610002</v>
       </c>
       <c r="E5" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F5" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.98426554165695</v>
+        <v>5.522443150519254</v>
       </c>
       <c r="D6" t="n">
-        <v>14.31039723208578</v>
+        <v>2.325439550213939</v>
       </c>
       <c r="E6" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F6" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.8741933145927</v>
+        <v>3.067056413621314</v>
       </c>
       <c r="D7" t="n">
-        <v>10.10088914733051</v>
+        <v>1.641394486441208</v>
       </c>
       <c r="E7" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F7" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.93720297320762</v>
+        <v>3.889795483146238</v>
       </c>
       <c r="D8" t="n">
-        <v>23.07404354622396</v>
+        <v>3.749532076261394</v>
       </c>
       <c r="E8" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F8" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.48819075118822</v>
+        <v>4.466830997068086</v>
       </c>
       <c r="D9" t="n">
-        <v>7.347133280968585</v>
+        <v>1.193909158157395</v>
       </c>
       <c r="E9" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F9" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>66.33011619593508</v>
+        <v>10.77864388183945</v>
       </c>
       <c r="D10" t="n">
-        <v>33.06496441320063</v>
+        <v>5.373056717145103</v>
       </c>
       <c r="E10" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F10" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.08181494297141</v>
+        <v>4.238294928232855</v>
       </c>
       <c r="D11" t="n">
-        <v>26.21925003607691</v>
+        <v>4.260628130862497</v>
       </c>
       <c r="E11" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F11" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>77.38423881878657</v>
+        <v>12.57493880805282</v>
       </c>
       <c r="D12" t="n">
-        <v>35.07653166346572</v>
+        <v>5.699936395313181</v>
       </c>
       <c r="E12" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F12" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.0763778522903</v>
+        <v>6.187411400997174</v>
       </c>
       <c r="D13" t="n">
-        <v>17.51373584232657</v>
+        <v>2.845982074378068</v>
       </c>
       <c r="E13" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F13" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>22.53921331294438</v>
+        <v>3.662622163353463</v>
       </c>
       <c r="D14" t="n">
-        <v>15.73762728487138</v>
+        <v>2.557364433791599</v>
       </c>
       <c r="E14" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F14" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>59.81907287443722</v>
+        <v>9.720599342096047</v>
       </c>
       <c r="D15" t="n">
-        <v>15.46606943128591</v>
+        <v>2.51323628258396</v>
       </c>
       <c r="E15" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F15" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>22.41315898972549</v>
+        <v>3.642138335830392</v>
       </c>
       <c r="D16" t="n">
-        <v>26.92305496946602</v>
+        <v>4.374996432538229</v>
       </c>
       <c r="E16" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F16" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>55.19514611852213</v>
+        <v>8.969211244259848</v>
       </c>
       <c r="D17" t="n">
-        <v>10.55139157151797</v>
+        <v>1.71460113037167</v>
       </c>
       <c r="E17" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F17" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>32.83545817478619</v>
+        <v>5.335761953402756</v>
       </c>
       <c r="D18" t="n">
-        <v>15.32038785248655</v>
+        <v>2.489563026029064</v>
       </c>
       <c r="E18" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F18" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>38.20859009473549</v>
+        <v>6.208895890394517</v>
       </c>
       <c r="D19" t="n">
-        <v>6.339075321158884</v>
+        <v>1.030099739688319</v>
       </c>
       <c r="E19" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F19" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>41.09694516626187</v>
+        <v>6.678253589517554</v>
       </c>
       <c r="D20" t="n">
-        <v>4.772607021092117</v>
+        <v>0.7755486409274691</v>
       </c>
       <c r="E20" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F20" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>58.12102860819432</v>
+        <v>9.444667148831577</v>
       </c>
       <c r="D21" t="n">
-        <v>21.6379417399114</v>
+        <v>3.516165532735603</v>
       </c>
       <c r="E21" t="n">
-        <v>19.8666414690694</v>
+        <v>3.228329238723777</v>
       </c>
       <c r="F21" t="n">
-        <v>9.803949035954302</v>
+        <v>1.593141718342574</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
